--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -825,7 +825,7 @@
         <v>127106255</v>
       </c>
       <c r="B3" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>127104398</v>
       </c>
       <c r="B4" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127104233</v>
       </c>
       <c r="B5" t="n">
-        <v>79598</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127104654</v>
       </c>
       <c r="B6" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>127104272</v>
       </c>
       <c r="B8" t="n">
-        <v>79569</v>
+        <v>79600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>127104492</v>
       </c>
       <c r="B11" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92727</v>
+        <v>92802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2151,10 +2151,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127105996</v>
+        <v>127105723</v>
       </c>
       <c r="B13" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2186,13 +2186,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529130</v>
+        <v>529161</v>
       </c>
       <c r="R13" t="n">
-        <v>6997165</v>
+        <v>6997137</v>
       </c>
       <c r="S13" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2221,7 +2221,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:53</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2231,12 +2231,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gott om långväxta bålar på en björk.</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2250,27 +2245,27 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>Bark på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>Bark on living woody plant # Betula</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2288,10 +2283,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127105723</v>
+        <v>127105996</v>
       </c>
       <c r="B14" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2323,13 +2318,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529161</v>
+        <v>529130</v>
       </c>
       <c r="R14" t="n">
-        <v>6997137</v>
+        <v>6997165</v>
       </c>
       <c r="S14" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2358,7 +2353,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2368,7 +2363,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:46</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Gott om långväxta bålar på en björk.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2382,27 +2382,27 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>127172776</v>
       </c>
       <c r="B16" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>127172771</v>
       </c>
       <c r="B17" t="n">
-        <v>78738</v>
+        <v>78769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91699</v>
+        <v>91773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127172770</v>
       </c>
       <c r="B19" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172765</v>
+        <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>75075</v>
+        <v>96689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529198</v>
+        <v>529173</v>
       </c>
       <c r="R20" t="n">
-        <v>6997089</v>
+        <v>6997063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172766</v>
+        <v>127172765</v>
       </c>
       <c r="B21" t="n">
-        <v>96614</v>
+        <v>75135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529173</v>
+        <v>529198</v>
       </c>
       <c r="R21" t="n">
-        <v>6997063</v>
+        <v>6997089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91245</v>
+        <v>91319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>127172774</v>
       </c>
       <c r="B24" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>127172775</v>
       </c>
       <c r="B25" t="n">
-        <v>78980</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>127172769</v>
       </c>
       <c r="B26" t="n">
-        <v>80083</v>
+        <v>80114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>127172777</v>
       </c>
       <c r="B27" t="n">
-        <v>82792</v>
+        <v>82852</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98361</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -825,7 +825,7 @@
         <v>127106255</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>127104398</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127104233</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127104654</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>127104272</v>
       </c>
       <c r="B8" t="n">
-        <v>79600</v>
+        <v>79603</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>127104492</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92802</v>
+        <v>92808</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127105723</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>127105996</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>127172776</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79014</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>127172771</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>78772</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91773</v>
+        <v>91779</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127172770</v>
       </c>
       <c r="B19" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>96689</v>
+        <v>96695</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127172765</v>
       </c>
       <c r="B21" t="n">
-        <v>75135</v>
+        <v>75138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91319</v>
+        <v>91325</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R24" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>98442</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R25" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>127172769</v>
       </c>
       <c r="B26" t="n">
-        <v>80114</v>
+        <v>80117</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>127172777</v>
       </c>
       <c r="B27" t="n">
-        <v>82852</v>
+        <v>82855</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98442</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172766</v>
+        <v>127172765</v>
       </c>
       <c r="B20" t="n">
-        <v>96695</v>
+        <v>75138</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529173</v>
+        <v>529198</v>
       </c>
       <c r="R20" t="n">
-        <v>6997063</v>
+        <v>6997089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172765</v>
+        <v>127172766</v>
       </c>
       <c r="B21" t="n">
-        <v>75138</v>
+        <v>96695</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529198</v>
+        <v>529173</v>
       </c>
       <c r="R21" t="n">
-        <v>6997089</v>
+        <v>6997063</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>98442</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R24" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B25" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R25" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92808</v>
+        <v>92809</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91779</v>
+        <v>91780</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127172766</v>
       </c>
       <c r="B21" t="n">
-        <v>96695</v>
+        <v>96696</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91325</v>
+        <v>91326</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B24" t="n">
-        <v>98442</v>
+        <v>79014</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R24" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B25" t="n">
-        <v>79014</v>
+        <v>98443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R25" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98442</v>
+        <v>98443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B8" t="n">
-        <v>79603</v>
+        <v>57657</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R8" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,12 +1586,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1604,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>79603</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,27 +1620,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1644,13 +1649,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R9" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,12 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172765</v>
+        <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>75138</v>
+        <v>96696</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529198</v>
+        <v>529173</v>
       </c>
       <c r="R20" t="n">
-        <v>6997089</v>
+        <v>6997063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172766</v>
+        <v>127172765</v>
       </c>
       <c r="B21" t="n">
-        <v>96696</v>
+        <v>75138</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529173</v>
+        <v>529198</v>
       </c>
       <c r="R21" t="n">
-        <v>6997063</v>
+        <v>6997089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127106485</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>127106255</v>
       </c>
       <c r="B3" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>127104398</v>
       </c>
       <c r="B4" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127104233</v>
       </c>
       <c r="B5" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127104654</v>
       </c>
       <c r="B6" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127104625</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>57821</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1470,7 +1470,7 @@
         <v>127103920</v>
       </c>
       <c r="B8" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>127104272</v>
       </c>
       <c r="B9" t="n">
-        <v>79603</v>
+        <v>79607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>127104492</v>
       </c>
       <c r="B11" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92809</v>
+        <v>92813</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127105723</v>
       </c>
       <c r="B13" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>127105996</v>
       </c>
       <c r="B14" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>127172776</v>
       </c>
       <c r="B16" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>127172771</v>
       </c>
       <c r="B17" t="n">
-        <v>78772</v>
+        <v>78776</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91780</v>
+        <v>91784</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127172770</v>
       </c>
       <c r="B19" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>96696</v>
+        <v>96700</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127172765</v>
       </c>
       <c r="B21" t="n">
-        <v>75138</v>
+        <v>75142</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>127172775</v>
       </c>
       <c r="B24" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>127172774</v>
       </c>
       <c r="B25" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>127172769</v>
       </c>
       <c r="B26" t="n">
-        <v>80117</v>
+        <v>80121</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>127172777</v>
       </c>
       <c r="B27" t="n">
-        <v>82855</v>
+        <v>82859</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98443</v>
+        <v>98447</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>79607</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R8" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,12 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,12 +1581,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1609,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>57661</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,27 +1615,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1649,13 +1644,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R9" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1689,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B8" t="n">
-        <v>79607</v>
+        <v>57661</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R8" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,12 +1586,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1604,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B9" t="n">
-        <v>57661</v>
+        <v>79607</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,27 +1620,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1644,13 +1649,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R9" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,12 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>127172774</v>
       </c>
       <c r="B25" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98447</v>
+        <v>98448</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B24" t="n">
-        <v>79018</v>
+        <v>98448</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R24" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B25" t="n">
-        <v>98448</v>
+        <v>79018</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R25" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127106485</v>
       </c>
       <c r="B2" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>127106255</v>
       </c>
       <c r="B3" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>127104398</v>
       </c>
       <c r="B4" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127104233</v>
       </c>
       <c r="B5" t="n">
-        <v>79636</v>
+        <v>79638</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127104654</v>
       </c>
       <c r="B6" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127104625</v>
       </c>
       <c r="B7" t="n">
-        <v>57821</v>
+        <v>57823</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B8" t="n">
-        <v>57661</v>
+        <v>79609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R8" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,12 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,12 +1581,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1609,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,27 +1615,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1649,13 +1644,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R9" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1689,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>127104492</v>
       </c>
       <c r="B11" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92813</v>
+        <v>92815</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127105723</v>
       </c>
       <c r="B13" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>127105996</v>
       </c>
       <c r="B14" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>127172776</v>
       </c>
       <c r="B16" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>127172771</v>
       </c>
       <c r="B17" t="n">
-        <v>78776</v>
+        <v>78778</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91784</v>
+        <v>91786</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127172770</v>
       </c>
       <c r="B19" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172766</v>
+        <v>127172765</v>
       </c>
       <c r="B20" t="n">
-        <v>96700</v>
+        <v>75144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529173</v>
+        <v>529198</v>
       </c>
       <c r="R20" t="n">
-        <v>6997063</v>
+        <v>6997089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172765</v>
+        <v>127172766</v>
       </c>
       <c r="B21" t="n">
-        <v>75142</v>
+        <v>96702</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529198</v>
+        <v>529173</v>
       </c>
       <c r="R21" t="n">
-        <v>6997089</v>
+        <v>6997063</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B24" t="n">
-        <v>98448</v>
+        <v>79020</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R24" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B25" t="n">
-        <v>79018</v>
+        <v>98450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R25" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>127172769</v>
       </c>
       <c r="B26" t="n">
-        <v>80121</v>
+        <v>80123</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>127172777</v>
       </c>
       <c r="B27" t="n">
-        <v>82859</v>
+        <v>82861</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98448</v>
+        <v>98450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B8" t="n">
-        <v>79609</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R8" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,12 +1586,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1604,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>79609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,27 +1620,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1644,13 +1649,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R9" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,12 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172765</v>
+        <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>75144</v>
+        <v>96702</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529198</v>
+        <v>529173</v>
       </c>
       <c r="R20" t="n">
-        <v>6997089</v>
+        <v>6997063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172766</v>
+        <v>127172765</v>
       </c>
       <c r="B21" t="n">
-        <v>96702</v>
+        <v>75144</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529173</v>
+        <v>529198</v>
       </c>
       <c r="R21" t="n">
-        <v>6997063</v>
+        <v>6997089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>79609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R8" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,12 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,12 +1581,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1609,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B9" t="n">
-        <v>79609</v>
+        <v>57663</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,27 +1615,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1649,13 +1644,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R9" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1689,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172766</v>
+        <v>127172765</v>
       </c>
       <c r="B20" t="n">
-        <v>96702</v>
+        <v>75144</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529173</v>
+        <v>529198</v>
       </c>
       <c r="R20" t="n">
-        <v>6997063</v>
+        <v>6997089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172765</v>
+        <v>127172766</v>
       </c>
       <c r="B21" t="n">
-        <v>75144</v>
+        <v>96702</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529198</v>
+        <v>529173</v>
       </c>
       <c r="R21" t="n">
-        <v>6997089</v>
+        <v>6997063</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B8" t="n">
-        <v>79609</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R8" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,12 +1586,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1604,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B9" t="n">
-        <v>57663</v>
+        <v>79609</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,27 +1620,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1644,13 +1649,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R9" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,12 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92815</v>
+        <v>92821</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91786</v>
+        <v>91792</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127172766</v>
       </c>
       <c r="B21" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B24" t="n">
-        <v>79020</v>
+        <v>98456</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R24" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B25" t="n">
-        <v>98450</v>
+        <v>79020</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R25" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98450</v>
+        <v>98456</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127106485</v>
       </c>
       <c r="B2" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>127106255</v>
       </c>
       <c r="B3" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>127104398</v>
       </c>
       <c r="B4" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127104233</v>
       </c>
       <c r="B5" t="n">
-        <v>79638</v>
+        <v>79641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127104654</v>
       </c>
       <c r="B6" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127104625</v>
       </c>
       <c r="B7" t="n">
-        <v>57823</v>
+        <v>57826</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>79612</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R8" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,12 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,12 +1581,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1609,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B9" t="n">
-        <v>79609</v>
+        <v>57666</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,27 +1615,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1649,13 +1644,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R9" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1689,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57663</v>
+        <v>57666</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>127104492</v>
       </c>
       <c r="B11" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92821</v>
+        <v>92824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127105723</v>
       </c>
       <c r="B13" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>127105996</v>
       </c>
       <c r="B14" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>127172776</v>
       </c>
       <c r="B16" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>127172771</v>
       </c>
       <c r="B17" t="n">
-        <v>78778</v>
+        <v>78781</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91792</v>
+        <v>91795</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127172770</v>
       </c>
       <c r="B19" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>127172765</v>
       </c>
       <c r="B20" t="n">
-        <v>75144</v>
+        <v>75147</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127172766</v>
       </c>
       <c r="B21" t="n">
-        <v>96708</v>
+        <v>96711</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B24" t="n">
-        <v>98456</v>
+        <v>79023</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R24" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B25" t="n">
-        <v>79020</v>
+        <v>98459</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R25" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>127172769</v>
       </c>
       <c r="B26" t="n">
-        <v>80123</v>
+        <v>80126</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>127172777</v>
       </c>
       <c r="B27" t="n">
-        <v>82861</v>
+        <v>82864</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98456</v>
+        <v>98459</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127106485</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>127106255</v>
       </c>
       <c r="B3" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>127104398</v>
       </c>
       <c r="B4" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127104233</v>
       </c>
       <c r="B5" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127104654</v>
       </c>
       <c r="B6" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127104625</v>
       </c>
       <c r="B7" t="n">
-        <v>57826</v>
+        <v>57832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B8" t="n">
-        <v>79612</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R8" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,12 +1586,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1604,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>79618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,27 +1620,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1644,13 +1649,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R9" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,12 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1885,7 +1885,7 @@
         <v>127104492</v>
       </c>
       <c r="B11" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92824</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127105723</v>
       </c>
       <c r="B13" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>127105996</v>
       </c>
       <c r="B14" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>127172776</v>
       </c>
       <c r="B16" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>127172771</v>
       </c>
       <c r="B17" t="n">
-        <v>78781</v>
+        <v>78787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91795</v>
+        <v>91803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127172770</v>
       </c>
       <c r="B19" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2939,10 +2939,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172765</v>
+        <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>75147</v>
+        <v>96719</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,21 +2950,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>53</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2974,10 +2974,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529198</v>
+        <v>529173</v>
       </c>
       <c r="R20" t="n">
-        <v>6997089</v>
+        <v>6997063</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,10 +3036,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172766</v>
+        <v>127172765</v>
       </c>
       <c r="B21" t="n">
-        <v>96711</v>
+        <v>75153</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3047,21 +3047,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>53</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3071,10 +3071,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529173</v>
+        <v>529198</v>
       </c>
       <c r="R21" t="n">
-        <v>6997063</v>
+        <v>6997089</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B24" t="n">
-        <v>79023</v>
+        <v>98467</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R24" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B25" t="n">
-        <v>98459</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R25" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>127172769</v>
       </c>
       <c r="B26" t="n">
-        <v>80126</v>
+        <v>80132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>127172777</v>
       </c>
       <c r="B27" t="n">
-        <v>82864</v>
+        <v>82870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98459</v>
+        <v>98467</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91803</v>
+        <v>91804</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>96719</v>
+        <v>96720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91349</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B24" t="n">
-        <v>98467</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R24" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B25" t="n">
-        <v>79029</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R25" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98467</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57689</v>
+        <v>57716</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -1749,7 +1749,7 @@
         <v>127105095</v>
       </c>
       <c r="B10" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127106485</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>127106255</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>127104398</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127104233</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>79629</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127104654</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127104625</v>
       </c>
       <c r="B7" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79600</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R8" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,12 +1552,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1586,12 +1581,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1609,10 +1604,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B9" t="n">
-        <v>79618</v>
+        <v>57657</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,27 +1615,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1649,13 +1644,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R9" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1684,7 +1679,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1694,7 +1689,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
         <v>127104492</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92832</v>
+        <v>92802</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127105723</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>127105996</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>98436</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>127172776</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>127172771</v>
       </c>
       <c r="B17" t="n">
-        <v>78787</v>
+        <v>78769</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91804</v>
+        <v>91773</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127172770</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>96720</v>
+        <v>96689</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127172765</v>
       </c>
       <c r="B21" t="n">
-        <v>75153</v>
+        <v>75135</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>91319</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>98436</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R24" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>79011</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R25" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>127172769</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>80114</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>127172777</v>
       </c>
       <c r="B27" t="n">
-        <v>82870</v>
+        <v>82852</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>98436</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127106485</v>
       </c>
       <c r="B2" t="n">
-        <v>57657</v>
+        <v>57672</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -825,7 +825,7 @@
         <v>127106255</v>
       </c>
       <c r="B3" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -957,7 +957,7 @@
         <v>127104398</v>
       </c>
       <c r="B4" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127104233</v>
       </c>
       <c r="B5" t="n">
-        <v>79629</v>
+        <v>79647</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>127104654</v>
       </c>
       <c r="B6" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>127104625</v>
       </c>
       <c r="B7" t="n">
-        <v>57817</v>
+        <v>57832</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1467,10 +1467,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127104272</v>
+        <v>127103920</v>
       </c>
       <c r="B8" t="n">
-        <v>79600</v>
+        <v>57672</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1478,27 +1478,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1507,13 +1507,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529126</v>
+        <v>529046</v>
       </c>
       <c r="R8" t="n">
-        <v>6997051</v>
+        <v>6997056</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,7 +1552,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1581,12 +1586,12 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1604,10 +1609,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127103920</v>
+        <v>127104272</v>
       </c>
       <c r="B9" t="n">
-        <v>57657</v>
+        <v>79618</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1615,27 +1620,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1644,13 +1649,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529046</v>
+        <v>529126</v>
       </c>
       <c r="R9" t="n">
-        <v>6997056</v>
+        <v>6997051</v>
       </c>
       <c r="S9" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1679,7 +1684,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1689,12 +1694,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1885,7 +1885,7 @@
         <v>127104492</v>
       </c>
       <c r="B11" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -2017,7 +2017,7 @@
         <v>127104088</v>
       </c>
       <c r="B12" t="n">
-        <v>92802</v>
+        <v>92832</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2154,7 +2154,7 @@
         <v>127105723</v>
       </c>
       <c r="B13" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2286,7 +2286,7 @@
         <v>127105996</v>
       </c>
       <c r="B14" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2423,7 +2423,7 @@
         <v>127104892</v>
       </c>
       <c r="B15" t="n">
-        <v>98436</v>
+        <v>98467</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2554,7 +2554,7 @@
         <v>127172776</v>
       </c>
       <c r="B16" t="n">
-        <v>79011</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>127172771</v>
       </c>
       <c r="B17" t="n">
-        <v>78769</v>
+        <v>78787</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2748,7 +2748,7 @@
         <v>127172768</v>
       </c>
       <c r="B18" t="n">
-        <v>91773</v>
+        <v>91804</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>127172770</v>
       </c>
       <c r="B19" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2942,7 +2942,7 @@
         <v>127172766</v>
       </c>
       <c r="B20" t="n">
-        <v>96689</v>
+        <v>96720</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>127172765</v>
       </c>
       <c r="B21" t="n">
-        <v>75135</v>
+        <v>75153</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3136,7 +3136,7 @@
         <v>127172767</v>
       </c>
       <c r="B22" t="n">
-        <v>91319</v>
+        <v>91350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>127172773</v>
       </c>
       <c r="B23" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,32 +3327,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172774</v>
+        <v>127172775</v>
       </c>
       <c r="B24" t="n">
-        <v>98436</v>
+        <v>79029</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529178</v>
+        <v>529199</v>
       </c>
       <c r="R24" t="n">
-        <v>6997069</v>
+        <v>6997059</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,32 +3424,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172775</v>
+        <v>127172774</v>
       </c>
       <c r="B25" t="n">
-        <v>79011</v>
+        <v>98468</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3459,10 +3459,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529199</v>
+        <v>529178</v>
       </c>
       <c r="R25" t="n">
-        <v>6997059</v>
+        <v>6997069</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3524,7 +3524,7 @@
         <v>127172769</v>
       </c>
       <c r="B26" t="n">
-        <v>80114</v>
+        <v>80132</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3621,7 +3621,7 @@
         <v>127172777</v>
       </c>
       <c r="B27" t="n">
-        <v>82852</v>
+        <v>82870</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3718,7 +3718,7 @@
         <v>127172772</v>
       </c>
       <c r="B28" t="n">
-        <v>98436</v>
+        <v>98468</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 38683-2022 artfynd.xlsx
+++ b/artfynd/A 38683-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY28"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127106485</v>
+        <v>127172766</v>
       </c>
       <c r="B2" t="n">
-        <v>57672</v>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,47 +686,37 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
+          <t>Adolfberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529108</v>
+        <v>529173</v>
       </c>
       <c r="R2" t="n">
-        <v>6997014</v>
+        <v>6997063</v>
       </c>
       <c r="S2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -753,26 +743,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>17:09</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre, på en tall.</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -781,51 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127106255</v>
+        <v>127172767</v>
       </c>
       <c r="B3" t="n">
-        <v>79029</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -833,37 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
+          <t>Adolfberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529108</v>
+        <v>529188</v>
       </c>
       <c r="R3" t="n">
-        <v>6997145</v>
+        <v>6997084</v>
       </c>
       <c r="S3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -890,21 +840,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>17:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -913,51 +853,26 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127104398</v>
+        <v>127172768</v>
       </c>
       <c r="B4" t="n">
-        <v>79029</v>
+        <v>92369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -965,34 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
+          <t>Adolfberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529161</v>
+        <v>529182</v>
       </c>
       <c r="R4" t="n">
-        <v>6997047</v>
+        <v>6997090</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1036,50 +951,25 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Pinus sylvestris</t>
-        </is>
-      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127104233</v>
+        <v>127172777</v>
       </c>
       <c r="B5" t="n">
-        <v>79647</v>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1087,42 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
+          <t>Adolfberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529126</v>
+        <v>529208</v>
       </c>
       <c r="R5" t="n">
-        <v>6997045</v>
+        <v>6997092</v>
       </c>
       <c r="S5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1149,21 +1034,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1172,51 +1047,26 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, markontakt</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127104654</v>
+        <v>127104088</v>
       </c>
       <c r="B6" t="n">
-        <v>79029</v>
+        <v>91962</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1224,37 +1074,42 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>2079</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529204</v>
+        <v>529105</v>
       </c>
       <c r="R6" t="n">
-        <v>6997067</v>
+        <v>6997072</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1281,14 +1136,19 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:42</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Långväxta bålar.</t>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1302,27 +1162,27 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Tallskog</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Liggande död trädstam, markontakt</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1340,58 +1200,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127104625</v>
+        <v>127104398</v>
       </c>
       <c r="B7" t="n">
-        <v>57832</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529191</v>
+        <v>529161</v>
       </c>
       <c r="R7" t="n">
-        <v>6997050</v>
+        <v>6997047</v>
       </c>
       <c r="S7" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1418,26 +1268,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>16:03</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Minst en talltita hördes. I äldre flerskiktad barrskog i storblockig sluttning.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1450,6 +1285,26 @@
       <c r="AH7" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1467,53 +1322,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127103920</v>
+        <v>127104492</v>
       </c>
       <c r="B8" t="n">
-        <v>57672</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>529046</v>
+        <v>529226</v>
       </c>
       <c r="R8" t="n">
-        <v>6997056</v>
+        <v>6997024</v>
       </c>
       <c r="S8" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1542,7 +1392,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1552,12 +1402,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack, äldre.</t>
+          <t>15:57</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1571,27 +1416,27 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>Trädstam på levande träd</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1609,50 +1454,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127104272</v>
+        <v>127104654</v>
       </c>
       <c r="B9" t="n">
-        <v>79618</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>529126</v>
+        <v>529204</v>
       </c>
       <c r="R9" t="n">
-        <v>6997051</v>
+        <v>6997067</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1682,19 +1522,14 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:49</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Långväxta bålar.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1708,27 +1543,27 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1746,67 +1581,48 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127105095</v>
+        <v>127105723</v>
       </c>
       <c r="B10" t="n">
-        <v>57723</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>529171</v>
+        <v>529161</v>
       </c>
       <c r="R10" t="n">
-        <v>6997087</v>
+        <v>6997137</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1835,7 +1651,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1845,12 +1661,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:15</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>En hona och hane som observerades i äldre barrblandskog med partier med minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1864,7 +1675,27 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>Barrskog</t>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>Gren på levande träd</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr"/>
@@ -1882,14 +1713,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127104492</v>
+        <v>127105996</v>
       </c>
       <c r="B11" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1917,13 +1748,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>529226</v>
+        <v>529130</v>
       </c>
       <c r="R11" t="n">
-        <v>6997024</v>
+        <v>6997165</v>
       </c>
       <c r="S11" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1952,7 +1783,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1962,7 +1793,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:57</t>
+          <t>16:53</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Gott om långväxta bålar på en björk.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1981,22 +1817,22 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>björkar</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Betula</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>Gren på levande träd</t>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>Branch on living tree # Picea abies</t>
+          <t>Bark on living woody plant # Betula</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr"/>
@@ -2014,53 +1850,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127104088</v>
+        <v>127106255</v>
       </c>
       <c r="B12" t="n">
-        <v>92832</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2079</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>529105</v>
+        <v>529108</v>
       </c>
       <c r="R12" t="n">
-        <v>6997072</v>
+        <v>6997145</v>
       </c>
       <c r="S12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2089,7 +1920,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -2099,7 +1930,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2113,27 +1944,27 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Barrskog</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, markontakt</t>
+          <t>Gren på levande träd</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+          <t>Branch on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr"/>
@@ -2151,14 +1982,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127105723</v>
+        <v>127172775</v>
       </c>
       <c r="B13" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -2182,17 +2013,17 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
+          <t>Adolfberget, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>529161</v>
+        <v>529199</v>
       </c>
       <c r="R13" t="n">
-        <v>6997137</v>
+        <v>6997059</v>
       </c>
       <c r="S13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2219,21 +2050,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>16:46</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2242,55 +2063,30 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>Gren på levande träd</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Branch on living tree # Picea abies</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127105996</v>
+        <v>127172776</v>
       </c>
       <c r="B14" t="n">
-        <v>79029</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2314,17 +2110,17 @@
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
+          <t>Adolfberget, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>529130</v>
+        <v>529190</v>
       </c>
       <c r="R14" t="n">
-        <v>6997165</v>
+        <v>6997060</v>
       </c>
       <c r="S14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2351,26 +2147,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>16:53</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Gott om långväxta bålar på en björk.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2379,103 +2160,64 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Betula</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127104892</v>
+        <v>127172765</v>
       </c>
       <c r="B15" t="n">
-        <v>98467</v>
+        <v>83307</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>500</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
+          <t>Adolfberget, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>529182</v>
+        <v>529198</v>
       </c>
       <c r="R15" t="n">
-        <v>6997056</v>
+        <v>6997089</v>
       </c>
       <c r="S15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2502,26 +2244,11 @@
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>16:12</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 500 plantor, 18 blomställningar och  8 vinterståndare inom ca 8 m2 yta i gammal barrskog i sluttning.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2530,31 +2257,26 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127172776</v>
+        <v>127172771</v>
       </c>
       <c r="B16" t="n">
-        <v>79029</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2562,21 +2284,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2586,10 +2308,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>529190</v>
+        <v>529188</v>
       </c>
       <c r="R16" t="n">
-        <v>6997060</v>
+        <v>6997100</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2648,10 +2370,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127172771</v>
+        <v>127104233</v>
       </c>
       <c r="B17" t="n">
-        <v>78787</v>
+        <v>79946</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2659,37 +2381,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Adolfberget, Jmt</t>
+          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>529188</v>
+        <v>529126</v>
       </c>
       <c r="R17" t="n">
-        <v>6997100</v>
+        <v>6997045</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2716,11 +2443,21 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
@@ -2729,48 +2466,73 @@
       </c>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127172768</v>
+        <v>119286175</v>
       </c>
       <c r="B18" t="n">
-        <v>91804</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2780,10 +2542,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>529182</v>
+        <v>529240</v>
       </c>
       <c r="R18" t="n">
-        <v>6997090</v>
+        <v>6997126</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2810,12 +2572,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2830,22 +2592,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127172770</v>
+        <v>127172769</v>
       </c>
       <c r="B19" t="n">
-        <v>80132</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2877,10 +2639,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>529208</v>
+        <v>529190</v>
       </c>
       <c r="R19" t="n">
-        <v>6997033</v>
+        <v>6997073</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2939,10 +2701,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127172766</v>
+        <v>127172770</v>
       </c>
       <c r="B20" t="n">
-        <v>96720</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2950,21 +2712,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>53</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2974,10 +2736,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>529173</v>
+        <v>529208</v>
       </c>
       <c r="R20" t="n">
-        <v>6997063</v>
+        <v>6997033</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -3036,32 +2798,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127172765</v>
+        <v>119286174</v>
       </c>
       <c r="B21" t="n">
-        <v>75153</v>
+        <v>80461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6440</v>
+        <v>6462</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -3071,10 +2833,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>529198</v>
+        <v>529240</v>
       </c>
       <c r="R21" t="n">
-        <v>6997089</v>
+        <v>6997126</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3101,12 +2863,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-08-02</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3121,22 +2883,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Noel Wieser</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127172767</v>
+        <v>127103920</v>
       </c>
       <c r="B22" t="n">
-        <v>91350</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3144,37 +2906,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Adolfberget, Jmt</t>
+          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>529188</v>
+        <v>529046</v>
       </c>
       <c r="R22" t="n">
-        <v>6997084</v>
+        <v>6997056</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3201,11 +2968,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre.</t>
+        </is>
+      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -3214,61 +2996,105 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM22" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127172773</v>
+        <v>127105095</v>
       </c>
       <c r="B23" t="n">
-        <v>98468</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Adolfberget, Jmt</t>
+          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>529177</v>
+        <v>529171</v>
       </c>
       <c r="R23" t="n">
-        <v>6997052</v>
+        <v>6997087</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3298,11 +3124,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>En hona och hane som observerades i äldre barrblandskog med partier med minst medelhöga livsmiljövärden för tretåig hackspett baserat på volymen stående död ved.</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
@@ -3311,26 +3152,31 @@
       </c>
       <c r="AG23" t="b">
         <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127172775</v>
+        <v>127106485</v>
       </c>
       <c r="B24" t="n">
-        <v>79029</v>
+        <v>57953</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3338,37 +3184,47 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Adolfberget, Jmt</t>
+          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>529199</v>
+        <v>529108</v>
       </c>
       <c r="R24" t="n">
-        <v>6997059</v>
+        <v>6997014</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3395,11 +3251,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:09</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på en tall.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3408,64 +3279,99 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AH24" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM24" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127172774</v>
+        <v>127104625</v>
       </c>
       <c r="B25" t="n">
-        <v>98468</v>
+        <v>58114</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Adolfberget, Jmt</t>
+          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>529178</v>
+        <v>529191</v>
       </c>
       <c r="R25" t="n">
-        <v>6997069</v>
+        <v>6997050</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3492,11 +3398,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>16:03</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Minst en talltita hördes. I äldre flerskiktad barrskog i storblockig sluttning.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3505,64 +3426,83 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127172769</v>
+        <v>127104892</v>
       </c>
       <c r="B26" t="n">
-        <v>80132</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Adolfberget, Jmt</t>
+          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>529190</v>
+        <v>529182</v>
       </c>
       <c r="R26" t="n">
-        <v>6997073</v>
+        <v>6997056</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3589,11 +3529,26 @@
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2025-08-02</t>
         </is>
       </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>16:12</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Minst 500 plantor, 18 blomställningar och  8 vinterståndare inom ca 8 m2 yta i gammal barrskog i sluttning.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3602,48 +3557,53 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AH26" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127172777</v>
+        <v>127172772</v>
       </c>
       <c r="B27" t="n">
-        <v>82870</v>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3653,10 +3613,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>529208</v>
+        <v>529206</v>
       </c>
       <c r="R27" t="n">
-        <v>6997092</v>
+        <v>6997079</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3715,10 +3675,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127172772</v>
+        <v>127172773</v>
       </c>
       <c r="B28" t="n">
-        <v>98468</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3750,10 +3710,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>529206</v>
+        <v>529177</v>
       </c>
       <c r="R28" t="n">
-        <v>6997079</v>
+        <v>6997052</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3809,6 +3769,240 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>127172774</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Adolfberget, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>529178</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6997069</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Marielle Löthman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>127104272</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Slåttflobäcken, Slåttflobäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>529126</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6997051</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Stugun</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-08-02</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM30" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, markontakt</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Horizontal, dead with ground contact # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
